--- a/Result/profitability/1617.xlsx
+++ b/Result/profitability/1617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08500000000000002</v>
+        <v>0.115</v>
       </c>
       <c r="N2" t="n">
-        <v>7.118749999999999</v>
+        <v>7.22125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="N3" t="n">
-        <v>7.015</v>
+        <v>7.08625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14625</v>
+        <v>0.1775</v>
       </c>
       <c r="N4" t="n">
-        <v>6.64625</v>
+        <v>6.635</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.89</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07499999999999998</v>
+        <v>-0.01499999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>3.28375</v>
+        <v>3.435</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.115</v>
+        <v>-0.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6550000000000002</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1325</v>
+        <v>-0.24875</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8837500000000003</v>
+        <v>1.06875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.29</v>
+        <v>-0.2837499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7750000000000002</v>
+        <v>0.7687500000000002</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.26625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6175000000000003</v>
+        <v>0.6175</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E75" t="n">
+        <v>91</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>29</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.5725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.04999999999999893</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.006045949214026458</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.371428571428571</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.210000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1726105563480742</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
